--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129688672</v>
+        <v>129688670</v>
       </c>
       <c r="B2" t="n">
-        <v>92864</v>
+        <v>97645</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672292</v>
+        <v>672165</v>
       </c>
       <c r="R2" t="n">
-        <v>7215610</v>
+        <v>7215594</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129688670</v>
+        <v>129688672</v>
       </c>
       <c r="B3" t="n">
-        <v>97634</v>
+        <v>92869</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672165</v>
+        <v>672292</v>
       </c>
       <c r="R3" t="n">
-        <v>7215594</v>
+        <v>7215610</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>129688669</v>
       </c>
       <c r="B4" t="n">
-        <v>79071</v>
+        <v>79075</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129688671</v>
       </c>
       <c r="B5" t="n">
-        <v>78828</v>
+        <v>78832</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129688670</v>
+        <v>129688672</v>
       </c>
       <c r="B2" t="n">
-        <v>97645</v>
+        <v>92870</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672165</v>
+        <v>672292</v>
       </c>
       <c r="R2" t="n">
-        <v>7215594</v>
+        <v>7215610</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129688672</v>
+        <v>129688670</v>
       </c>
       <c r="B3" t="n">
-        <v>92869</v>
+        <v>97646</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672292</v>
+        <v>672165</v>
       </c>
       <c r="R3" t="n">
-        <v>7215610</v>
+        <v>7215594</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,7 +890,7 @@
         <v>129688669</v>
       </c>
       <c r="B4" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129688671</v>
       </c>
       <c r="B5" t="n">
-        <v>78832</v>
+        <v>78833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688672</v>
       </c>
       <c r="B2" t="n">
-        <v>92870</v>
+        <v>92875</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688670</v>
       </c>
       <c r="B3" t="n">
-        <v>97646</v>
+        <v>97651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129688669</v>
       </c>
       <c r="B4" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129688671</v>
       </c>
       <c r="B5" t="n">
-        <v>78833</v>
+        <v>78838</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688672</v>
       </c>
       <c r="B2" t="n">
-        <v>92875</v>
+        <v>92879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688670</v>
       </c>
       <c r="B3" t="n">
-        <v>97651</v>
+        <v>97655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688672</v>
       </c>
       <c r="B2" t="n">
-        <v>92879</v>
+        <v>92881</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688670</v>
       </c>
       <c r="B3" t="n">
-        <v>97655</v>
+        <v>97657</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>129688670</v>
       </c>
       <c r="B3" t="n">
-        <v>97657</v>
+        <v>97667</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688672</v>
       </c>
       <c r="B2" t="n">
-        <v>92881</v>
+        <v>92884</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688670</v>
       </c>
       <c r="B3" t="n">
-        <v>97667</v>
+        <v>97671</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129688669</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129688671</v>
       </c>
       <c r="B5" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688672</v>
       </c>
       <c r="B2" t="n">
-        <v>92884</v>
+        <v>92887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688670</v>
       </c>
       <c r="B3" t="n">
-        <v>97671</v>
+        <v>97674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129688669</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129688671</v>
       </c>
       <c r="B5" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129688672</v>
+        <v>129688670</v>
       </c>
       <c r="B2" t="n">
-        <v>92887</v>
+        <v>97674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672292</v>
+        <v>672165</v>
       </c>
       <c r="R2" t="n">
-        <v>7215610</v>
+        <v>7215594</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129688670</v>
+        <v>129688672</v>
       </c>
       <c r="B3" t="n">
-        <v>97674</v>
+        <v>92887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672165</v>
+        <v>672292</v>
       </c>
       <c r="R3" t="n">
-        <v>7215594</v>
+        <v>7215610</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129688670</v>
+        <v>129688672</v>
       </c>
       <c r="B2" t="n">
-        <v>97674</v>
+        <v>92887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>672165</v>
+        <v>672292</v>
       </c>
       <c r="R2" t="n">
-        <v>7215594</v>
+        <v>7215610</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129688672</v>
+        <v>129688670</v>
       </c>
       <c r="B3" t="n">
-        <v>92887</v>
+        <v>97674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672292</v>
+        <v>672165</v>
       </c>
       <c r="R3" t="n">
-        <v>7215610</v>
+        <v>7215594</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688672</v>
       </c>
       <c r="B2" t="n">
-        <v>92887</v>
+        <v>92888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688670</v>
       </c>
       <c r="B3" t="n">
-        <v>97674</v>
+        <v>97675</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129688669</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129688671</v>
       </c>
       <c r="B5" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129688672</v>
       </c>
       <c r="B2" t="n">
-        <v>92888</v>
+        <v>92905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>129688670</v>
       </c>
       <c r="B3" t="n">
-        <v>97675</v>
+        <v>97692</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>129688669</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129688671</v>
       </c>
       <c r="B5" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -678,11 +678,11 @@
         <v>129688672</v>
       </c>
       <c r="B2" t="n">
-        <v>92905</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129688670</v>
+        <v>129688669</v>
       </c>
       <c r="B3" t="n">
-        <v>97692</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>672165</v>
+        <v>672172</v>
       </c>
       <c r="R3" t="n">
-        <v>7215594</v>
+        <v>7215579</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129688669</v>
+        <v>129688671</v>
       </c>
       <c r="B4" t="n">
-        <v>79089</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>672172</v>
+        <v>672232</v>
       </c>
       <c r="R4" t="n">
-        <v>7215579</v>
+        <v>7215710</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129688671</v>
+        <v>129688670</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>97989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>672232</v>
+        <v>672165</v>
       </c>
       <c r="R5" t="n">
-        <v>7215710</v>
+        <v>7215594</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 43680-2025 artfynd.xlsx
+++ b/artfynd/A 43680-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688672</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688669</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688671</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129688670</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>